--- a/research/traditional_assets/database/data/thailand/thailand_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0583</v>
+        <v>-0.00211</v>
       </c>
       <c r="E2">
-        <v>0.113</v>
+        <v>0.0189</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>7.38021661845533e-05</v>
+        <v>0.0001558025929686038</v>
       </c>
       <c r="J2">
-        <v>6.402009773434716e-05</v>
+        <v>0.0001307214715183463</v>
       </c>
       <c r="K2">
-        <v>152.94</v>
+        <v>81.89500000000001</v>
       </c>
       <c r="L2">
-        <v>0.08595940225223302</v>
+        <v>0.1879187700780175</v>
       </c>
       <c r="M2">
-        <v>66.43000000000001</v>
+        <v>73.03999999999999</v>
       </c>
       <c r="N2">
-        <v>0.02310930216377931</v>
+        <v>0.02432153441443841</v>
       </c>
       <c r="O2">
-        <v>0.4343533411795476</v>
+        <v>0.8918737407656143</v>
       </c>
       <c r="P2">
-        <v>66.43000000000001</v>
+        <v>73.03999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.02310930216377931</v>
+        <v>0.02432153441443841</v>
       </c>
       <c r="R2">
-        <v>0.4343533411795476</v>
+        <v>0.8918737407656143</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>277.11</v>
+        <v>253.04</v>
       </c>
       <c r="V2">
-        <v>0.0963994990607389</v>
+        <v>0.0842595984149712</v>
       </c>
       <c r="W2">
-        <v>0.1017082785808147</v>
+        <v>0.05732538330494038</v>
       </c>
       <c r="X2">
-        <v>0.04834024898199724</v>
+        <v>0.09457077607249646</v>
       </c>
       <c r="Y2">
-        <v>0.05336802959881749</v>
+        <v>-0.03724539276755608</v>
       </c>
       <c r="Z2">
-        <v>1.208329114375982</v>
+        <v>0.1842870153418092</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04374866144426875</v>
+        <v>0.08229198394287902</v>
       </c>
       <c r="AC2">
-        <v>-0.04374866144426875</v>
+        <v>-0.08229198394287902</v>
       </c>
       <c r="AD2">
-        <v>1273.949</v>
+        <v>1036.387</v>
       </c>
       <c r="AE2">
-        <v>0.2634515014922429</v>
+        <v>0.1255061499214124</v>
       </c>
       <c r="AF2">
-        <v>1274.212451501492</v>
+        <v>1036.512506149921</v>
       </c>
       <c r="AG2">
-        <v>997.1024515014923</v>
+        <v>783.4725061499214</v>
       </c>
       <c r="AH2">
-        <v>0.3071270312641738</v>
+        <v>0.2565871119004436</v>
       </c>
       <c r="AI2">
-        <v>0.4792411931055593</v>
+        <v>0.4022928294257653</v>
       </c>
       <c r="AJ2">
-        <v>0.2575359196610794</v>
+        <v>0.2069080956135008</v>
       </c>
       <c r="AK2">
-        <v>0.4186511421159645</v>
+        <v>0.3371989571971153</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-2.16</v>
+        <v>-1.66</v>
       </c>
       <c r="AN2">
-        <v>6923.635869565218</v>
+        <v>11143.94623655914</v>
       </c>
       <c r="AP2">
-        <v>5419.03506250811</v>
+        <v>8424.435549999154</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XSpring Capital Public Company Limited (SET:XPG)</t>
+          <t>Beyond Securities Public Company Limited (SET:BYD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.21</v>
-      </c>
-      <c r="E3">
-        <v>-0.249</v>
+        <v>-0.302</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,16 +728,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.03116694387909599</v>
+        <v>0.0004837611562685964</v>
       </c>
       <c r="J3">
-        <v>0.03116694387909599</v>
+        <v>0.0004837611562685964</v>
       </c>
       <c r="K3">
-        <v>0.79</v>
+        <v>-1.93</v>
       </c>
       <c r="L3">
-        <v>0.2762237762237763</v>
+        <v>-0.5693215339233038</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +746,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,61 +755,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>81</v>
+        <v>67.5</v>
       </c>
       <c r="V3">
-        <v>0.1046241281322656</v>
+        <v>0.04184489492281942</v>
       </c>
       <c r="W3">
-        <v>0.009645909645909646</v>
+        <v>-0.04519906323185011</v>
       </c>
       <c r="X3">
-        <v>0.04049801811754344</v>
+        <v>0.07838742817839225</v>
       </c>
       <c r="Y3">
-        <v>-0.03085210847163379</v>
+        <v>-0.1235864914102424</v>
       </c>
       <c r="Z3">
-        <v>0.04103340318729182</v>
+        <v>0.09973286816509852</v>
       </c>
       <c r="AA3">
-        <v>0.001278885774306643</v>
+        <v>4.824688762153155e-05</v>
       </c>
       <c r="AB3">
-        <v>0.04048312641374912</v>
+        <v>0.07838909305213096</v>
       </c>
       <c r="AC3">
-        <v>-0.03920424063944248</v>
+        <v>-0.07834084616450943</v>
       </c>
       <c r="AD3">
-        <v>2.23</v>
+        <v>0.257</v>
       </c>
       <c r="AE3">
-        <v>0.1693127025289274</v>
+        <v>0.001800248401247292</v>
       </c>
       <c r="AF3">
-        <v>2.399312702528928</v>
+        <v>0.2588002484012473</v>
       </c>
       <c r="AG3">
-        <v>-78.60068729747107</v>
+        <v>-67.24119975159876</v>
       </c>
       <c r="AH3">
-        <v>0.003089511751149293</v>
+        <v>0.0001604108449784394</v>
       </c>
       <c r="AI3">
-        <v>0.00789768969911483</v>
+        <v>0.0008111365309458945</v>
       </c>
       <c r="AJ3">
-        <v>-0.112997074410688</v>
+        <v>-0.04349763363949792</v>
       </c>
       <c r="AK3">
-        <v>-0.3527869379131119</v>
+        <v>-0.2672981413697377</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>18.13008130081301</v>
+        <v>128.5</v>
       </c>
       <c r="AP3">
-        <v>-639.0299780282201</v>
+        <v>-33620.59987579938</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Beyond Securities Public Company Limited (SET:BYD)</t>
+          <t>XSpring Capital Public Company Limited (SET:XPG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,7 +841,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.5570000000000001</v>
+        <v>-0.29</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.02491249461000874</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.02491249461000874</v>
       </c>
       <c r="K4">
-        <v>-6.65</v>
+        <v>-2.49</v>
       </c>
       <c r="L4">
-        <v>-20.03012048192771</v>
+        <v>-1.753521126760564</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,61 +883,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9.32</v>
+        <v>34.5</v>
       </c>
       <c r="V4">
-        <v>0.01115633229590615</v>
+        <v>0.08273381294964029</v>
       </c>
       <c r="W4">
-        <v>-0.2982062780269059</v>
+        <v>-0.008261446582614468</v>
       </c>
       <c r="X4">
-        <v>0.04044998065664608</v>
+        <v>0.07868139833893911</v>
       </c>
       <c r="Y4">
-        <v>-0.3386562586835519</v>
+        <v>-0.08694284492155357</v>
       </c>
       <c r="Z4">
-        <v>0.01537820186205938</v>
+        <v>0.006376058456179873</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.0001588435219226817</v>
       </c>
       <c r="AB4">
-        <v>0.0404465044071367</v>
+        <v>0.07853175430301347</v>
       </c>
       <c r="AC4">
-        <v>-0.0404465044071367</v>
+        <v>-0.07837291078109079</v>
       </c>
       <c r="AD4">
-        <v>0.609</v>
+        <v>3.86</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.07812128826893794</v>
       </c>
       <c r="AF4">
-        <v>0.609</v>
+        <v>3.938121288268938</v>
       </c>
       <c r="AG4">
-        <v>-8.711</v>
+        <v>-30.56187871173106</v>
       </c>
       <c r="AH4">
-        <v>0.0007284610572374221</v>
+        <v>0.009355582421987422</v>
       </c>
       <c r="AI4">
-        <v>0.01406174236301923</v>
+        <v>0.0137870998118439</v>
       </c>
       <c r="AJ4">
-        <v>-0.01053721532523113</v>
+        <v>-0.07908608656373474</v>
       </c>
       <c r="AK4">
-        <v>-0.2562887993174262</v>
+        <v>-0.1216935069632483</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>75.68627450980392</v>
+      </c>
+      <c r="AP4">
+        <v>-599.2525237594326</v>
       </c>
     </row>
     <row r="5">
@@ -960,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.12</v>
+        <v>0.0391</v>
       </c>
       <c r="E5">
-        <v>0.113</v>
+        <v>0.0189</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.0003011100454562346</v>
+        <v>0.0005469603000971541</v>
       </c>
       <c r="J5">
-        <v>0.0002370962802370203</v>
+        <v>0.0004266796785480114</v>
       </c>
       <c r="K5">
-        <v>10.7</v>
+        <v>6.73</v>
       </c>
       <c r="L5">
-        <v>0.2215320910973085</v>
+        <v>0.1809139784946237</v>
       </c>
       <c r="M5">
-        <v>1.49</v>
+        <v>2.13</v>
       </c>
       <c r="N5">
-        <v>0.01883691529709229</v>
+        <v>0.02791612057667104</v>
       </c>
       <c r="O5">
-        <v>0.1392523364485981</v>
+        <v>0.3164933135215453</v>
       </c>
       <c r="P5">
-        <v>1.49</v>
+        <v>2.13</v>
       </c>
       <c r="Q5">
-        <v>0.01883691529709229</v>
+        <v>0.02791612057667104</v>
       </c>
       <c r="R5">
-        <v>0.1392523364485981</v>
+        <v>0.3164933135215453</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>29.4</v>
+        <v>24.5</v>
       </c>
       <c r="V5">
-        <v>0.3716814159292036</v>
+        <v>0.3211009174311927</v>
       </c>
       <c r="W5">
-        <v>0.09312445604873802</v>
+        <v>0.05732538330494038</v>
       </c>
       <c r="X5">
-        <v>0.04082654794079778</v>
+        <v>0.07958310521030189</v>
       </c>
       <c r="Y5">
-        <v>0.05229790810794024</v>
+        <v>-0.02225772190536151</v>
       </c>
       <c r="Z5">
-        <v>0.8015628726981227</v>
+        <v>0.4624952104370958</v>
       </c>
       <c r="AA5">
-        <v>0.0001900475754928251</v>
+        <v>0.0001973373077192949</v>
       </c>
       <c r="AB5">
-        <v>0.04068285034339857</v>
+        <v>0.07885472703383407</v>
       </c>
       <c r="AC5">
-        <v>-0.04049280276790575</v>
+        <v>-0.07865738972611477</v>
       </c>
       <c r="AD5">
-        <v>1.51</v>
+        <v>2.87</v>
       </c>
       <c r="AE5">
-        <v>0.01728192402231934</v>
+        <v>0.02326538418192933</v>
       </c>
       <c r="AF5">
-        <v>1.527281924022319</v>
+        <v>2.893265384181929</v>
       </c>
       <c r="AG5">
-        <v>-27.87271807597768</v>
+        <v>-21.60673461581807</v>
       </c>
       <c r="AH5">
-        <v>0.01894249548758851</v>
+        <v>0.03653423520480102</v>
       </c>
       <c r="AI5">
-        <v>0.01284214941528754</v>
+        <v>0.02583428007261745</v>
       </c>
       <c r="AJ5">
-        <v>-0.5440991016723681</v>
+        <v>-0.3950529277059228</v>
       </c>
       <c r="AK5">
-        <v>-0.3113321154956091</v>
+        <v>-0.2469531171449956</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1065,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>83.8888888888889</v>
+        <v>114.8</v>
       </c>
       <c r="AP5">
-        <v>-1548.484337554316</v>
+        <v>-864.2693846327228</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Country Group Holdings Public Company Limited (SET:CGH)</t>
+          <t>KGI Securities (Thailand) Public Company Limited (SET:KGI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1091,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.109</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="E6">
-        <v>0.167</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,100 +1103,97 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0004098619600114491</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.000382014879474786</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>19.5</v>
+        <v>33.2</v>
       </c>
       <c r="L6">
-        <v>0.3939393939393939</v>
+        <v>0.2964285714285714</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>29</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.1006594932315168</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.8734939759036143</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>29</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.1006594932315168</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.8734939759036143</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>36.3</v>
+        <v>16.3</v>
       </c>
       <c r="V6">
-        <v>0.2307692307692307</v>
+        <v>0.05657757723012843</v>
       </c>
       <c r="W6">
-        <v>0.1172579675285628</v>
+        <v>0.1549230051329911</v>
       </c>
       <c r="X6">
-        <v>0.04829038289037816</v>
+        <v>0.09411086977654189</v>
       </c>
       <c r="Y6">
-        <v>0.06896758463818467</v>
+        <v>0.06081213535644926</v>
       </c>
       <c r="Z6">
-        <v>0.2871836729284769</v>
+        <v>0.2856377755958225</v>
       </c>
       <c r="AA6">
-        <v>0.0001097084362008985</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04305494141005158</v>
+        <v>0.08062899424064626</v>
       </c>
       <c r="AC6">
-        <v>-0.04294523297385067</v>
+        <v>-0.08062899424064626</v>
       </c>
       <c r="AD6">
-        <v>60.9</v>
+        <v>143.1</v>
       </c>
       <c r="AE6">
-        <v>0.06355916489716637</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>60.96355916489716</v>
+        <v>143.1</v>
       </c>
       <c r="AG6">
-        <v>24.66355916489717</v>
+        <v>126.8</v>
       </c>
       <c r="AH6">
-        <v>0.2793116697911054</v>
+        <v>0.3318645640074211</v>
       </c>
       <c r="AI6">
-        <v>0.2606800280582053</v>
+        <v>0.4216263995285798</v>
       </c>
       <c r="AJ6">
-        <v>0.1355411999967906</v>
+        <v>0.3056158110388045</v>
       </c>
       <c r="AK6">
-        <v>0.1248386052020435</v>
+        <v>0.3924481584648715</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1845.454545454545</v>
-      </c>
-      <c r="AP6">
-        <v>747.3805807544595</v>
       </c>
     </row>
     <row r="7">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finansia Syrus Securities Public Company Limited (SET:FSS)</t>
+          <t>FNS Holdings Public Company Limited (SET:FNS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0583</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="E7">
-        <v>0.079</v>
+        <v>-0.306</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,28 +1231,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7.74</v>
+        <v>0.465</v>
       </c>
       <c r="L7">
-        <v>0.1134897360703812</v>
+        <v>0.0727699530516432</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>4.58</v>
       </c>
       <c r="N7">
-        <v>0.01248499399759904</v>
+        <v>0.1339181286549707</v>
       </c>
       <c r="O7">
-        <v>0.1343669250645995</v>
+        <v>9.849462365591398</v>
       </c>
       <c r="P7">
-        <v>1.04</v>
+        <v>4.58</v>
       </c>
       <c r="Q7">
-        <v>0.01248499399759904</v>
+        <v>0.1339181286549707</v>
       </c>
       <c r="R7">
-        <v>0.1343669250645995</v>
+        <v>9.849462365591398</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1261,55 +1261,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V7">
-        <v>0.1200480192076831</v>
+        <v>0.4678362573099415</v>
       </c>
       <c r="W7">
-        <v>0.1017082785808147</v>
+        <v>0.005871212121212122</v>
       </c>
       <c r="X7">
-        <v>0.04644509316683446</v>
+        <v>0.09967811388807558</v>
       </c>
       <c r="Y7">
-        <v>0.05526318541398027</v>
+        <v>-0.09380690176686346</v>
       </c>
       <c r="Z7">
-        <v>1.049230769230769</v>
+        <v>0.06288132257429639</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04342516686110874</v>
+        <v>0.08110445771347408</v>
       </c>
       <c r="AC7">
-        <v>-0.04342516686110874</v>
+        <v>-0.08110445771347408</v>
       </c>
       <c r="AD7">
-        <v>24.7</v>
+        <v>23</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>24.7</v>
+        <v>23</v>
       </c>
       <c r="AG7">
-        <v>14.7</v>
+        <v>7</v>
       </c>
       <c r="AH7">
-        <v>0.2287037037037037</v>
+        <v>0.4020979020979021</v>
       </c>
       <c r="AI7">
-        <v>0.2407407407407407</v>
+        <v>0.253025302530253</v>
       </c>
       <c r="AJ7">
-        <v>0.15</v>
+        <v>0.1699029126213592</v>
       </c>
       <c r="AK7">
-        <v>0.1587473002159827</v>
+        <v>0.09345794392523364</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KGI Securities (Thailand) Public Company Limited (SET:KGI)</t>
+          <t>Asia Plus Group Holdings Public Company Limited (SET:ASP)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.14</v>
+        <v>-0.00211</v>
       </c>
       <c r="E8">
-        <v>0.187</v>
+        <v>-0.0851</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,28 +1353,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>57.9</v>
+        <v>13</v>
       </c>
       <c r="L8">
-        <v>0.3616489693941287</v>
+        <v>0.2034428794992175</v>
       </c>
       <c r="M8">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="N8">
-        <v>0.03934077618288145</v>
+        <v>0.08319559228650138</v>
       </c>
       <c r="O8">
-        <v>0.2556131260794474</v>
+        <v>1.161538461538461</v>
       </c>
       <c r="P8">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="Q8">
-        <v>0.03934077618288145</v>
+        <v>0.08319559228650138</v>
       </c>
       <c r="R8">
-        <v>0.2556131260794474</v>
+        <v>1.161538461538461</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1383,55 +1383,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>26.9</v>
+        <v>39.9</v>
       </c>
       <c r="V8">
-        <v>0.07150451887293992</v>
+        <v>0.2198347107438016</v>
       </c>
       <c r="W8">
-        <v>0.3186571271326362</v>
+        <v>0.09021512838306732</v>
       </c>
       <c r="X8">
-        <v>0.05150673045909023</v>
+        <v>0.1216677714713185</v>
       </c>
       <c r="Y8">
-        <v>0.267150396673546</v>
+        <v>-0.03145264308825121</v>
       </c>
       <c r="Z8">
-        <v>0.666378083195285</v>
+        <v>0.2149344096871847</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04374866144426875</v>
+        <v>0.08229198394287902</v>
       </c>
       <c r="AC8">
-        <v>-0.04374866144426875</v>
+        <v>-0.08229198394287902</v>
       </c>
       <c r="AD8">
-        <v>205.5</v>
+        <v>248.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>205.5</v>
+        <v>248.1</v>
       </c>
       <c r="AG8">
-        <v>178.6</v>
+        <v>208.2</v>
       </c>
       <c r="AH8">
-        <v>0.3532748839608045</v>
+        <v>0.5775139664804468</v>
       </c>
       <c r="AI8">
-        <v>0.4894022386282448</v>
+        <v>0.6663980660757454</v>
       </c>
       <c r="AJ8">
-        <v>0.3219178082191781</v>
+        <v>0.5342571208622017</v>
       </c>
       <c r="AK8">
-        <v>0.4544529262086514</v>
+        <v>0.6263537906137184</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.065</v>
+        <v>-0.584</v>
       </c>
       <c r="E9">
-        <v>0.296</v>
+        <v>0.377</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,28 +1475,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3.86</v>
+        <v>1.99</v>
       </c>
       <c r="L9">
-        <v>0.00317355915481378</v>
+        <v>0.1137142857142857</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>3.24</v>
       </c>
       <c r="N9">
-        <v>0.02335600907029478</v>
+        <v>0.1182481751824818</v>
       </c>
       <c r="O9">
-        <v>0.266839378238342</v>
+        <v>1.628140703517588</v>
       </c>
       <c r="P9">
-        <v>1.03</v>
+        <v>3.24</v>
       </c>
       <c r="Q9">
-        <v>0.02335600907029478</v>
+        <v>0.1182481751824818</v>
       </c>
       <c r="R9">
-        <v>0.266839378238342</v>
+        <v>1.628140703517588</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1505,61 +1505,61 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>15.7</v>
+        <v>13.4</v>
       </c>
       <c r="V9">
-        <v>0.3560090702947846</v>
+        <v>0.489051094890511</v>
       </c>
       <c r="W9">
-        <v>0.08616071428571428</v>
+        <v>0.04392935982339956</v>
       </c>
       <c r="X9">
-        <v>0.04834024898199724</v>
+        <v>0.09248175345755488</v>
       </c>
       <c r="Y9">
-        <v>0.03782046530371704</v>
+        <v>-0.04855239363415532</v>
       </c>
       <c r="Z9">
-        <v>36.44890620317651</v>
+        <v>0.3739316239316239</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04410346757111569</v>
+        <v>0.08236576148557441</v>
       </c>
       <c r="AC9">
-        <v>-0.04410346757111569</v>
+        <v>-0.08236576148557441</v>
       </c>
       <c r="AD9">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="AG9">
-        <v>1.5</v>
+        <v>-1.200000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.2805872756933116</v>
+        <v>0.3080808080808081</v>
       </c>
       <c r="AI9">
-        <v>0.2743221690590111</v>
+        <v>0.2359767891682785</v>
       </c>
       <c r="AJ9">
-        <v>0.03289473684210526</v>
+        <v>-0.0458015267175573</v>
       </c>
       <c r="AK9">
-        <v>0.03191489361702127</v>
+        <v>-0.03133159268929507</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-2.16</v>
+        <v>-1.66</v>
       </c>
       <c r="AQ9">
         <v>-0</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Asia Plus Group Holdings Public Company Limited (SET:ASP)</t>
+          <t>Finansia Syrus Securities Public Company Limited (SET:FSS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.07820000000000001</v>
+        <v>0.0623</v>
       </c>
       <c r="E10">
-        <v>0.0658</v>
+        <v>0.0354</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1600,28 +1600,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>27</v>
+        <v>5.67</v>
       </c>
       <c r="L10">
-        <v>0.2746693794506612</v>
+        <v>0.09725557461406519</v>
       </c>
       <c r="M10">
-        <v>20</v>
+        <v>1.54</v>
       </c>
       <c r="N10">
-        <v>0.09153318077803203</v>
+        <v>0.02659758203799655</v>
       </c>
       <c r="O10">
-        <v>0.7407407407407407</v>
+        <v>0.2716049382716049</v>
       </c>
       <c r="P10">
-        <v>20</v>
+        <v>1.54</v>
       </c>
       <c r="Q10">
-        <v>0.09153318077803203</v>
+        <v>0.02659758203799655</v>
       </c>
       <c r="R10">
-        <v>0.7407407407407407</v>
+        <v>0.2716049382716049</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1630,55 +1630,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>33.5</v>
+        <v>5.19</v>
       </c>
       <c r="V10">
-        <v>0.1533180778032037</v>
+        <v>0.08963730569948188</v>
       </c>
       <c r="W10">
-        <v>0.1830508474576271</v>
+        <v>0.07278562259306803</v>
       </c>
       <c r="X10">
-        <v>0.05775358641127933</v>
+        <v>0.09457077607249646</v>
       </c>
       <c r="Y10">
-        <v>0.1252972610463478</v>
+        <v>-0.02178515347942843</v>
       </c>
       <c r="Z10">
-        <v>0.5833827893175074</v>
+        <v>0.6295896328293735</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0447567931404327</v>
+        <v>0.08275630394454861</v>
       </c>
       <c r="AC10">
-        <v>-0.0447567931404327</v>
+        <v>-0.08275630394454861</v>
       </c>
       <c r="AD10">
-        <v>186.7</v>
+        <v>29.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>186.7</v>
+        <v>29.6</v>
       </c>
       <c r="AG10">
-        <v>153.2</v>
+        <v>24.41</v>
       </c>
       <c r="AH10">
-        <v>0.4607601184600197</v>
+        <v>0.3382857142857143</v>
       </c>
       <c r="AI10">
-        <v>0.5643893591293834</v>
+        <v>0.2862669245647969</v>
       </c>
       <c r="AJ10">
-        <v>0.4121603443637342</v>
+        <v>0.2965617786417203</v>
       </c>
       <c r="AK10">
-        <v>0.5153044063235789</v>
+        <v>0.2485490275939314</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finansa Public Company Limited (SET:FNS)</t>
+          <t>Maybank Securities (Thailand) Public Company Limited (SET:MST)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,7 +1704,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.138</v>
+        <v>-0.0152</v>
+      </c>
+      <c r="E11">
+        <v>-0.0242</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,28 +1722,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-1.16</v>
+        <v>17.1</v>
       </c>
       <c r="L11">
-        <v>-0.1286031042128603</v>
+        <v>0.2310810810810811</v>
       </c>
       <c r="M11">
-        <v>6.69</v>
+        <v>12.2</v>
       </c>
       <c r="N11">
-        <v>0.1612048192771084</v>
+        <v>0.06538049303322616</v>
       </c>
       <c r="O11">
-        <v>-5.767241379310345</v>
+        <v>0.7134502923976607</v>
       </c>
       <c r="P11">
-        <v>6.69</v>
+        <v>12.2</v>
       </c>
       <c r="Q11">
-        <v>0.1612048192771084</v>
+        <v>0.06538049303322616</v>
       </c>
       <c r="R11">
-        <v>-5.767241379310345</v>
+        <v>0.7134502923976607</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1749,55 +1752,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9.109999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="V11">
-        <v>0.2195180722891566</v>
+        <v>0.05048231511254019</v>
       </c>
       <c r="W11">
-        <v>-0.01273326015367728</v>
+        <v>0.123021582733813</v>
       </c>
       <c r="X11">
-        <v>0.0581149052337692</v>
+        <v>0.1459735552471633</v>
       </c>
       <c r="Y11">
-        <v>-0.07084816538744648</v>
+        <v>-0.02295197251335031</v>
       </c>
       <c r="Z11">
-        <v>0.07326185834957764</v>
+        <v>0.09948910997579993</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04480494950732253</v>
+        <v>0.08299236487683384</v>
       </c>
       <c r="AC11">
-        <v>-0.04480494950732253</v>
+        <v>-0.08299236487683384</v>
       </c>
       <c r="AD11">
-        <v>36.2</v>
+        <v>398.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>36.2</v>
+        <v>398.3</v>
       </c>
       <c r="AG11">
-        <v>27.09</v>
+        <v>388.88</v>
       </c>
       <c r="AH11">
-        <v>0.4658944658944659</v>
+        <v>0.6809711061719953</v>
       </c>
       <c r="AI11">
-        <v>0.3136915077989602</v>
+        <v>0.7555007587253414</v>
       </c>
       <c r="AJ11">
-        <v>0.3949555328765126</v>
+        <v>0.6757489400152915</v>
       </c>
       <c r="AK11">
-        <v>0.2548687552921253</v>
+        <v>0.7510525705898258</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1814,7 +1817,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trinity Watthana Public Company Limited (SET:TNITY)</t>
+          <t>Country Group Holdings Public Company Limited (SET:CGH)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1823,10 +1826,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0776</v>
+        <v>0.236</v>
       </c>
       <c r="E12">
-        <v>0.161</v>
+        <v>-0.104</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1835,103 +1838,94 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.0002455002672653527</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.0002020488925281221</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>9.26</v>
+        <v>2.95</v>
       </c>
       <c r="L12">
-        <v>0.3096989966555184</v>
+        <v>0.07248157248157248</v>
       </c>
       <c r="M12">
-        <v>4.78</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.08255613126079447</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.5161987041036717</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>4.78</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.08255613126079447</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.5161987041036717</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>1.58</v>
+        <v>24.3</v>
       </c>
       <c r="V12">
-        <v>0.02728842832469776</v>
+        <v>0.3131443298969073</v>
       </c>
       <c r="W12">
-        <v>0.2044150110375276</v>
+        <v>0.01710144927536232</v>
       </c>
       <c r="X12">
-        <v>0.07870083354250286</v>
+        <v>0.101234012530035</v>
       </c>
       <c r="Y12">
-        <v>0.1257141774950247</v>
+        <v>-0.08413256325467264</v>
       </c>
       <c r="Z12">
-        <v>0.2287448983677697</v>
+        <v>0.206494165398275</v>
       </c>
       <c r="AA12">
-        <v>4.621765338666572e-05</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04656676056530741</v>
+        <v>0.08380201145306046</v>
       </c>
       <c r="AC12">
-        <v>-0.04652054291192075</v>
+        <v>-0.08380201145306046</v>
       </c>
       <c r="AD12">
-        <v>109.3</v>
+        <v>56</v>
       </c>
       <c r="AE12">
-        <v>0.01329771004382977</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>109.3132977100438</v>
+        <v>56</v>
       </c>
       <c r="AG12">
-        <v>107.7332977100438</v>
+        <v>31.7</v>
       </c>
       <c r="AH12">
-        <v>0.6537356729821723</v>
+        <v>0.4191616766467066</v>
       </c>
       <c r="AI12">
-        <v>0.685722579485642</v>
+        <v>0.2650260293421675</v>
       </c>
       <c r="AJ12">
-        <v>0.6504326074497458</v>
+        <v>0.2900274473924977</v>
       </c>
       <c r="AK12">
-        <v>0.6825764859070554</v>
+        <v>0.1695187165775401</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>10930</v>
-      </c>
-      <c r="AP12">
-        <v>10773.32977100438</v>
       </c>
     </row>
     <row r="13">
@@ -1942,7 +1936,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maybank Securities (Thailand) Public Company Limited (SET:MST)</t>
+          <t>Trinity Watthana Public Company Limited (SET:TNITY)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1951,10 +1945,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.00121</v>
+        <v>0.0471</v>
       </c>
       <c r="E13">
-        <v>-0.0323</v>
+        <v>0.425</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1963,34 +1957,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.0005017216279114492</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.0004129493967486019</v>
       </c>
       <c r="K13">
-        <v>24</v>
+        <v>5.21</v>
       </c>
       <c r="L13">
-        <v>0.2489626556016597</v>
+        <v>0.2480952380952381</v>
       </c>
       <c r="M13">
-        <v>16.6</v>
+        <v>5.25</v>
       </c>
       <c r="N13">
-        <v>0.08015451472718495</v>
+        <v>0.1209677419354839</v>
       </c>
       <c r="O13">
-        <v>0.6916666666666668</v>
+        <v>1.00767754318618</v>
       </c>
       <c r="P13">
-        <v>16.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q13">
-        <v>0.08015451472718495</v>
+        <v>0.1209677419354839</v>
       </c>
       <c r="R13">
-        <v>0.6916666666666668</v>
+        <v>1.00767754318618</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1999,61 +1993,67 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>24.3</v>
+        <v>2.03</v>
       </c>
       <c r="V13">
-        <v>0.1173346209560599</v>
+        <v>0.04677419354838709</v>
       </c>
       <c r="W13">
-        <v>0.1711840228245364</v>
+        <v>0.1039920159680639</v>
       </c>
       <c r="X13">
-        <v>0.1020030572611921</v>
+        <v>0.1652973906156521</v>
       </c>
       <c r="Y13">
-        <v>0.06918096556334433</v>
+        <v>-0.06130537464758826</v>
       </c>
       <c r="Z13">
-        <v>0.2487164271524033</v>
+        <v>0.1343292295768305</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>5.547117431945661e-05</v>
       </c>
       <c r="AB13">
-        <v>0.04749152070256613</v>
+        <v>0.0878593481048511</v>
       </c>
       <c r="AC13">
-        <v>-0.04749152070256613</v>
+        <v>-0.08780387693053164</v>
       </c>
       <c r="AD13">
-        <v>629.1</v>
+        <v>119.1</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>0.02231922906929783</v>
       </c>
       <c r="AF13">
-        <v>629.1</v>
+        <v>119.1223192290693</v>
       </c>
       <c r="AG13">
-        <v>604.8000000000001</v>
+        <v>117.0923192290693</v>
       </c>
       <c r="AH13">
-        <v>0.7523319779956948</v>
+        <v>0.7329597546609626</v>
       </c>
       <c r="AI13">
-        <v>0.8190339799505273</v>
+        <v>0.7280322133944298</v>
       </c>
       <c r="AJ13">
-        <v>0.7449193250400296</v>
+        <v>0.7295820746533324</v>
       </c>
       <c r="AK13">
-        <v>0.8131218069373488</v>
+        <v>0.7246156239832297</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>7940</v>
+      </c>
+      <c r="AP13">
+        <v>7806.154615271286</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00211</v>
+        <v>0.0001050000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0189</v>
+        <v>-0.00984</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001558025929686038</v>
+        <v>0.0002461189680876223</v>
       </c>
       <c r="J2">
-        <v>0.0001307214715183463</v>
+        <v>0.0002102182520449734</v>
       </c>
       <c r="K2">
-        <v>81.89500000000001</v>
+        <v>46.41</v>
       </c>
       <c r="L2">
-        <v>0.1879187700780175</v>
+        <v>0.1319553040857525</v>
       </c>
       <c r="M2">
-        <v>73.03999999999999</v>
+        <v>52.35</v>
       </c>
       <c r="N2">
-        <v>0.02432153441443841</v>
+        <v>0.02725568803040558</v>
       </c>
       <c r="O2">
-        <v>0.8918737407656143</v>
+        <v>1.127989657401422</v>
       </c>
       <c r="P2">
-        <v>73.03999999999999</v>
+        <v>52.35</v>
       </c>
       <c r="Q2">
-        <v>0.02432153441443841</v>
+        <v>0.02725568803040558</v>
       </c>
       <c r="R2">
-        <v>0.8918737407656143</v>
+        <v>1.127989657401422</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>253.04</v>
+        <v>185.8</v>
       </c>
       <c r="V2">
-        <v>0.0842595984149712</v>
+        <v>0.09673556515853594</v>
       </c>
       <c r="W2">
-        <v>0.05732538330494038</v>
+        <v>0.02965216215018553</v>
       </c>
       <c r="X2">
-        <v>0.09457077607249646</v>
+        <v>0.08603355906683796</v>
       </c>
       <c r="Y2">
-        <v>-0.03724539276755608</v>
+        <v>-0.05638139691665243</v>
       </c>
       <c r="Z2">
-        <v>0.1842870153418092</v>
+        <v>0.1588891223940528</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08229198394287902</v>
+        <v>0.06936687827464189</v>
       </c>
       <c r="AC2">
-        <v>-0.08229198394287902</v>
+        <v>-0.06936687827464189</v>
       </c>
       <c r="AD2">
-        <v>1036.387</v>
+        <v>1384.008</v>
       </c>
       <c r="AE2">
-        <v>0.1255061499214124</v>
+        <v>0.2171874886695119</v>
       </c>
       <c r="AF2">
-        <v>1036.512506149921</v>
+        <v>1384.225187488669</v>
       </c>
       <c r="AG2">
-        <v>783.4725061499214</v>
+        <v>1198.42518748867</v>
       </c>
       <c r="AH2">
-        <v>0.2565871119004436</v>
+        <v>0.418837071631418</v>
       </c>
       <c r="AI2">
-        <v>0.4022928294257653</v>
+        <v>0.4594594930985139</v>
       </c>
       <c r="AJ2">
-        <v>0.2069080956135008</v>
+        <v>0.3842183674755193</v>
       </c>
       <c r="AK2">
-        <v>0.3371989571971153</v>
+        <v>0.423932402878091</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.66</v>
+        <v>-2.37</v>
       </c>
       <c r="AN2">
-        <v>11143.94623655914</v>
+        <v>10646.21538461539</v>
       </c>
       <c r="AP2">
-        <v>8424.435549999154</v>
+        <v>9218.655288374381</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Beyond Securities Public Company Limited (SET:BYD)</t>
+          <t>XSpring Capital Public Company Limited (SET:XPG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,9 +718,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.302</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -728,16 +725,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.0004837611562685964</v>
+        <v>0.005579910892668337</v>
       </c>
       <c r="J3">
-        <v>0.0004837611562685964</v>
+        <v>0.003328705463557318</v>
       </c>
       <c r="K3">
-        <v>-1.93</v>
+        <v>0.86</v>
       </c>
       <c r="L3">
-        <v>-0.5693215339233038</v>
+        <v>0.06825396825396826</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,61 +752,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>67.5</v>
+        <v>34.4</v>
       </c>
       <c r="V3">
-        <v>0.04184489492281942</v>
+        <v>0.09289765055360517</v>
       </c>
       <c r="W3">
-        <v>-0.04519906323185011</v>
+        <v>0.003052893148739794</v>
       </c>
       <c r="X3">
-        <v>0.07838742817839225</v>
+        <v>0.06588246216386848</v>
       </c>
       <c r="Y3">
-        <v>-0.1235864914102424</v>
+        <v>-0.06282956901512868</v>
       </c>
       <c r="Z3">
-        <v>0.09973286816509852</v>
+        <v>0.05014756406006594</v>
       </c>
       <c r="AA3">
-        <v>4.824688762153155e-05</v>
+        <v>0.0001669264704708321</v>
       </c>
       <c r="AB3">
-        <v>0.07838909305213096</v>
+        <v>0.06576627045786546</v>
       </c>
       <c r="AC3">
-        <v>-0.07834084616450943</v>
+        <v>-0.06559934398739463</v>
       </c>
       <c r="AD3">
-        <v>0.257</v>
+        <v>3.66</v>
       </c>
       <c r="AE3">
-        <v>0.001800248401247292</v>
+        <v>0.1984656137618947</v>
       </c>
       <c r="AF3">
-        <v>0.2588002484012473</v>
+        <v>3.858465613761895</v>
       </c>
       <c r="AG3">
-        <v>-67.24119975159876</v>
+        <v>-30.54153438623811</v>
       </c>
       <c r="AH3">
-        <v>0.0001604108449784394</v>
+        <v>0.01031238357104268</v>
       </c>
       <c r="AI3">
-        <v>0.0008111365309458945</v>
+        <v>0.01317968928984753</v>
       </c>
       <c r="AJ3">
-        <v>-0.04349763363949792</v>
+        <v>-0.08989190109234181</v>
       </c>
       <c r="AK3">
-        <v>-0.2672981413697377</v>
+        <v>-0.1182137938220177</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>128.5</v>
+        <v>33.27272727272727</v>
       </c>
       <c r="AP3">
-        <v>-33620.59987579938</v>
+        <v>-277.6503126021646</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XSpring Capital Public Company Limited (SET:XPG)</t>
+          <t>Beyond Securities Public Company Limited (SET:BYD)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,26 +837,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.29</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0.02491249461000874</v>
-      </c>
-      <c r="J4">
-        <v>0.02491249461000874</v>
-      </c>
       <c r="K4">
-        <v>-2.49</v>
-      </c>
-      <c r="L4">
-        <v>-1.753521126760564</v>
+        <v>-16.9</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,67 +862,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>34.5</v>
+        <v>37.3</v>
       </c>
       <c r="V4">
-        <v>0.08273381294964029</v>
+        <v>0.05585504642108416</v>
       </c>
       <c r="W4">
-        <v>-0.008261446582614468</v>
+        <v>-0.05301129234629862</v>
       </c>
       <c r="X4">
-        <v>0.07868139833893911</v>
+        <v>0.06567974414388103</v>
       </c>
       <c r="Y4">
-        <v>-0.08694284492155357</v>
+        <v>-0.1186910364901796</v>
       </c>
       <c r="Z4">
-        <v>0.006376058456179873</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.0001588435219226817</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07853175430301347</v>
+        <v>0.06566885276359893</v>
       </c>
       <c r="AC4">
-        <v>-0.07837291078109079</v>
+        <v>-0.06566885276359893</v>
       </c>
       <c r="AD4">
-        <v>3.86</v>
+        <v>0.658</v>
       </c>
       <c r="AE4">
-        <v>0.07812128826893794</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.938121288268938</v>
+        <v>0.658</v>
       </c>
       <c r="AG4">
-        <v>-30.56187871173106</v>
+        <v>-36.642</v>
       </c>
       <c r="AH4">
-        <v>0.009355582421987422</v>
+        <v>0.0009843550380128595</v>
       </c>
       <c r="AI4">
-        <v>0.0137870998118439</v>
+        <v>0.00205139076811802</v>
       </c>
       <c r="AJ4">
-        <v>-0.07908608656373474</v>
+        <v>-0.05805519378665881</v>
       </c>
       <c r="AK4">
-        <v>-0.1216935069632483</v>
+        <v>-0.1292678280380162</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>75.68627450980392</v>
-      </c>
-      <c r="AP4">
-        <v>-599.2525237594326</v>
       </c>
     </row>
     <row r="5">
@@ -963,10 +936,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0391</v>
+        <v>0.0133</v>
       </c>
       <c r="E5">
-        <v>0.0189</v>
+        <v>-0.128</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +948,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.0005469603000971541</v>
+        <v>0.0002013080497644157</v>
       </c>
       <c r="J5">
-        <v>0.0004266796785480114</v>
+        <v>0.0001575864577062067</v>
       </c>
       <c r="K5">
-        <v>6.73</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>0.1809139784946237</v>
+        <v>0.09287925696594428</v>
       </c>
       <c r="M5">
-        <v>2.13</v>
+        <v>1.24</v>
       </c>
       <c r="N5">
-        <v>0.02791612057667104</v>
+        <v>0.01751412429378531</v>
       </c>
       <c r="O5">
-        <v>0.3164933135215453</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="P5">
-        <v>2.13</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>0.02791612057667104</v>
+        <v>0.01751412429378531</v>
       </c>
       <c r="R5">
-        <v>0.3164933135215453</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +984,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>24.5</v>
+        <v>19.7</v>
       </c>
       <c r="V5">
-        <v>0.3211009174311927</v>
+        <v>0.2782485875706215</v>
       </c>
       <c r="W5">
-        <v>0.05732538330494038</v>
+        <v>0.02749770852428965</v>
       </c>
       <c r="X5">
-        <v>0.07958310521030189</v>
+        <v>0.06644687588549786</v>
       </c>
       <c r="Y5">
-        <v>-0.02225772190536151</v>
+        <v>-0.03894916736120821</v>
       </c>
       <c r="Z5">
-        <v>0.4624952104370958</v>
+        <v>0.4055878771041105</v>
       </c>
       <c r="AA5">
-        <v>0.0001973373077192949</v>
+        <v>6.391515684141707e-05</v>
       </c>
       <c r="AB5">
-        <v>0.07885472703383407</v>
+        <v>0.06602816281301238</v>
       </c>
       <c r="AC5">
-        <v>-0.07865738972611477</v>
+        <v>-0.06596424765617097</v>
       </c>
       <c r="AD5">
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="AE5">
-        <v>0.02326538418192933</v>
+        <v>0.007488749963046869</v>
       </c>
       <c r="AF5">
-        <v>2.893265384181929</v>
+        <v>2.597488749963047</v>
       </c>
       <c r="AG5">
-        <v>-21.60673461581807</v>
+        <v>-17.10251125003695</v>
       </c>
       <c r="AH5">
-        <v>0.03653423520480102</v>
+        <v>0.03538934089164399</v>
       </c>
       <c r="AI5">
-        <v>0.02583428007261745</v>
+        <v>0.02218227545006909</v>
       </c>
       <c r="AJ5">
-        <v>-0.3950529277059228</v>
+        <v>-0.318497412973502</v>
       </c>
       <c r="AK5">
-        <v>-0.2469531171449956</v>
+        <v>-0.1755949919195781</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>114.8</v>
+        <v>323.75</v>
       </c>
       <c r="AP5">
-        <v>-864.2693846327228</v>
+        <v>-2137.813906254619</v>
       </c>
     </row>
     <row r="6">
@@ -1091,10 +1064,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.07240000000000001</v>
+        <v>0.00392</v>
       </c>
       <c r="E6">
-        <v>0.06309999999999999</v>
+        <v>-0.068</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1082,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>33.2</v>
+        <v>21.2</v>
       </c>
       <c r="L6">
-        <v>0.2964285714285714</v>
+        <v>0.2217573221757322</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>19.3</v>
       </c>
       <c r="N6">
-        <v>0.1006594932315168</v>
+        <v>0.07231172723866618</v>
       </c>
       <c r="O6">
-        <v>0.8734939759036143</v>
+        <v>0.9103773584905661</v>
       </c>
       <c r="P6">
-        <v>29</v>
+        <v>19.3</v>
       </c>
       <c r="Q6">
-        <v>0.1006594932315168</v>
+        <v>0.07231172723866618</v>
       </c>
       <c r="R6">
-        <v>0.8734939759036143</v>
+        <v>0.9103773584905661</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1112,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>16.3</v>
+        <v>20.9</v>
       </c>
       <c r="V6">
-        <v>0.05657757723012843</v>
+        <v>0.07830648182840015</v>
       </c>
       <c r="W6">
-        <v>0.1549230051329911</v>
+        <v>0.1081081081081081</v>
       </c>
       <c r="X6">
-        <v>0.09411086977654189</v>
+        <v>0.08049569491871063</v>
       </c>
       <c r="Y6">
-        <v>0.06081213535644926</v>
+        <v>0.02761241318939749</v>
       </c>
       <c r="Z6">
-        <v>0.2856377755958225</v>
+        <v>0.2967174852262006</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08062899424064626</v>
+        <v>0.06802520432608085</v>
       </c>
       <c r="AC6">
-        <v>-0.08062899424064626</v>
+        <v>-0.06802520432608085</v>
       </c>
       <c r="AD6">
-        <v>143.1</v>
+        <v>184.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>143.1</v>
+        <v>184.3</v>
       </c>
       <c r="AG6">
-        <v>126.8</v>
+        <v>163.4</v>
       </c>
       <c r="AH6">
-        <v>0.3318645640074211</v>
+        <v>0.4084663120567376</v>
       </c>
       <c r="AI6">
-        <v>0.4216263995285798</v>
+        <v>0.473657157543048</v>
       </c>
       <c r="AJ6">
-        <v>0.3056158110388045</v>
+        <v>0.3797350685568209</v>
       </c>
       <c r="AK6">
-        <v>0.3924481584648715</v>
+        <v>0.4437805540467137</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1177,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FNS Holdings Public Company Limited (SET:FNS)</t>
+          <t>Asia Plus Group Holdings Public Company Limited (SET:ASP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,10 +1186,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.07679999999999999</v>
+        <v>-0.00371</v>
       </c>
       <c r="E7">
-        <v>-0.306</v>
+        <v>-0.0252</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,28 +1204,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.465</v>
+        <v>14.5</v>
       </c>
       <c r="L7">
-        <v>0.0727699530516432</v>
+        <v>0.2223926380368098</v>
       </c>
       <c r="M7">
-        <v>4.58</v>
+        <v>12.1</v>
       </c>
       <c r="N7">
-        <v>0.1339181286549707</v>
+        <v>0.06918238993710692</v>
       </c>
       <c r="O7">
-        <v>9.849462365591398</v>
+        <v>0.8344827586206897</v>
       </c>
       <c r="P7">
-        <v>4.58</v>
+        <v>12.1</v>
       </c>
       <c r="Q7">
-        <v>0.1339181286549707</v>
+        <v>0.06918238993710692</v>
       </c>
       <c r="R7">
-        <v>9.849462365591398</v>
+        <v>0.8344827586206897</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1261,55 +1234,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>16</v>
+        <v>29.7</v>
       </c>
       <c r="V7">
-        <v>0.4678362573099415</v>
+        <v>0.169811320754717</v>
       </c>
       <c r="W7">
-        <v>0.005871212121212122</v>
+        <v>0.1167471819645733</v>
       </c>
       <c r="X7">
-        <v>0.09967811388807558</v>
+        <v>0.09863211583173009</v>
       </c>
       <c r="Y7">
-        <v>-0.09380690176686346</v>
+        <v>0.01811506613284317</v>
       </c>
       <c r="Z7">
-        <v>0.06288132257429639</v>
+        <v>0.1961492178098676</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08110445771347408</v>
+        <v>0.0691665696360379</v>
       </c>
       <c r="AC7">
-        <v>-0.08110445771347408</v>
+        <v>-0.0691665696360379</v>
       </c>
       <c r="AD7">
-        <v>23</v>
+        <v>268.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>23</v>
+        <v>268.4</v>
       </c>
       <c r="AG7">
-        <v>7</v>
+        <v>238.7</v>
       </c>
       <c r="AH7">
-        <v>0.4020979020979021</v>
+        <v>0.6054590570719603</v>
       </c>
       <c r="AI7">
-        <v>0.253025302530253</v>
+        <v>0.6711677919479869</v>
       </c>
       <c r="AJ7">
-        <v>0.1699029126213592</v>
+        <v>0.577127659574468</v>
       </c>
       <c r="AK7">
-        <v>0.09345794392523364</v>
+        <v>0.6447866018368449</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1326,7 +1299,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Asia Plus Group Holdings Public Company Limited (SET:ASP)</t>
+          <t>Maybank Securities (Thailand) Public Company Limited (SET:MST)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1335,10 +1308,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.00211</v>
+        <v>-0.0269</v>
       </c>
       <c r="E8">
-        <v>-0.0851</v>
+        <v>0.005520000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,28 +1326,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="L8">
-        <v>0.2034428794992175</v>
+        <v>0.2074882995319813</v>
       </c>
       <c r="M8">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="N8">
-        <v>0.08319559228650138</v>
+        <v>0.08481152993348115</v>
       </c>
       <c r="O8">
-        <v>1.161538461538461</v>
+        <v>1.150375939849624</v>
       </c>
       <c r="P8">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="Q8">
-        <v>0.08319559228650138</v>
+        <v>0.08481152993348115</v>
       </c>
       <c r="R8">
-        <v>1.161538461538461</v>
+        <v>1.150375939849624</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1383,55 +1356,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>39.9</v>
+        <v>10.7</v>
       </c>
       <c r="V8">
-        <v>0.2198347107438016</v>
+        <v>0.05931263858093126</v>
       </c>
       <c r="W8">
-        <v>0.09021512838306732</v>
+        <v>0.1031807602792863</v>
       </c>
       <c r="X8">
-        <v>0.1216677714713185</v>
+        <v>0.1102044979052564</v>
       </c>
       <c r="Y8">
-        <v>-0.03145264308825121</v>
+        <v>-0.007023737625970125</v>
       </c>
       <c r="Z8">
-        <v>0.2149344096871847</v>
+        <v>0.1237977519409788</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08229198394287902</v>
+        <v>0.06956718691324587</v>
       </c>
       <c r="AC8">
-        <v>-0.08229198394287902</v>
+        <v>-0.06956718691324587</v>
       </c>
       <c r="AD8">
-        <v>248.1</v>
+        <v>374</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>248.1</v>
+        <v>374</v>
       </c>
       <c r="AG8">
-        <v>208.2</v>
+        <v>363.3</v>
       </c>
       <c r="AH8">
-        <v>0.5775139664804468</v>
+        <v>0.6746031746031746</v>
       </c>
       <c r="AI8">
-        <v>0.6663980660757454</v>
+        <v>0.7397151898734177</v>
       </c>
       <c r="AJ8">
-        <v>0.5342571208622017</v>
+        <v>0.6681993746551407</v>
       </c>
       <c r="AK8">
-        <v>0.6263537906137184</v>
+        <v>0.7340876944837341</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,7 +1421,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Globlex Holding Management Public Company Limited (SET:GBX)</t>
+          <t>Country Group Holdings Public Company Limited (SET:CGH)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1457,10 +1430,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.584</v>
-      </c>
-      <c r="E9">
-        <v>0.377</v>
+        <v>0.164</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,94 +1445,88 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1.99</v>
+        <v>-6.89</v>
       </c>
       <c r="L9">
-        <v>0.1137142857142857</v>
+        <v>-0.2100609756097561</v>
       </c>
       <c r="M9">
-        <v>3.24</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.1182481751824818</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>1.628140703517588</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>3.24</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.1182481751824818</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>1.628140703517588</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>13.4</v>
+        <v>15.8</v>
       </c>
       <c r="V9">
-        <v>0.489051094890511</v>
+        <v>0.1926829268292683</v>
       </c>
       <c r="W9">
-        <v>0.04392935982339956</v>
+        <v>-0.0444516129032258</v>
       </c>
       <c r="X9">
-        <v>0.09248175345755488</v>
+        <v>0.08182612314144257</v>
       </c>
       <c r="Y9">
-        <v>-0.04855239363415532</v>
+        <v>-0.1262777360446684</v>
       </c>
       <c r="Z9">
-        <v>0.3739316239316239</v>
+        <v>0.175682913765399</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.08236576148557441</v>
+        <v>0.07014268383035602</v>
       </c>
       <c r="AC9">
-        <v>-0.08236576148557441</v>
+        <v>-0.07014268383035602</v>
       </c>
       <c r="AD9">
-        <v>12.2</v>
+        <v>61.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>12.2</v>
+        <v>61.7</v>
       </c>
       <c r="AG9">
-        <v>-1.200000000000001</v>
+        <v>45.90000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.3080808080808081</v>
+        <v>0.4293667362560891</v>
       </c>
       <c r="AI9">
-        <v>0.2359767891682785</v>
+        <v>0.2884525479195886</v>
       </c>
       <c r="AJ9">
-        <v>-0.0458015267175573</v>
+        <v>0.3588741204065677</v>
       </c>
       <c r="AK9">
-        <v>-0.03133159268929507</v>
+        <v>0.231701161029783</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1.66</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1573,7 +1537,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finansia Syrus Securities Public Company Limited (SET:FSS)</t>
+          <t>FNS Holdings Public Company Limited (SET:FNS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1582,10 +1546,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0623</v>
+        <v>0.235</v>
       </c>
       <c r="E10">
-        <v>0.0354</v>
+        <v>0.735</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1600,28 +1564,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>5.67</v>
+        <v>23.7</v>
       </c>
       <c r="L10">
-        <v>0.09725557461406519</v>
+        <v>0.7899999999999999</v>
       </c>
       <c r="M10">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="N10">
-        <v>0.02659758203799655</v>
+        <v>0.03208828522920203</v>
       </c>
       <c r="O10">
-        <v>0.2716049382716049</v>
+        <v>0.07974683544303797</v>
       </c>
       <c r="P10">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
-        <v>0.02659758203799655</v>
+        <v>0.03208828522920203</v>
       </c>
       <c r="R10">
-        <v>0.2716049382716049</v>
+        <v>0.07974683544303797</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1630,55 +1594,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>5.19</v>
+        <v>3.91</v>
       </c>
       <c r="V10">
-        <v>0.08963730569948188</v>
+        <v>0.06638370118845502</v>
       </c>
       <c r="W10">
-        <v>0.07278562259306803</v>
+        <v>0.3490427098674521</v>
       </c>
       <c r="X10">
-        <v>0.09457077607249646</v>
+        <v>0.1932664326782276</v>
       </c>
       <c r="Y10">
-        <v>-0.02178515347942843</v>
+        <v>0.1557762771892245</v>
       </c>
       <c r="Z10">
-        <v>0.6295896328293735</v>
+        <v>0.4070556309362279</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.08275630394454861</v>
+        <v>0.07061752117646683</v>
       </c>
       <c r="AC10">
-        <v>-0.08275630394454861</v>
+        <v>-0.07061752117646683</v>
       </c>
       <c r="AD10">
-        <v>29.6</v>
+        <v>349.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>29.6</v>
+        <v>349.8</v>
       </c>
       <c r="AG10">
-        <v>24.41</v>
+        <v>345.89</v>
       </c>
       <c r="AH10">
-        <v>0.3382857142857143</v>
+        <v>0.8558845118668951</v>
       </c>
       <c r="AI10">
-        <v>0.2862669245647969</v>
+        <v>0.6284584980237155</v>
       </c>
       <c r="AJ10">
-        <v>0.2965617786417203</v>
+        <v>0.8544924528768003</v>
       </c>
       <c r="AK10">
-        <v>0.2485490275939314</v>
+        <v>0.6258300313014528</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1695,7 +1659,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maybank Securities (Thailand) Public Company Limited (SET:MST)</t>
+          <t>Globlex Holding Management Public Company Limited (SET:GBX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,10 +1668,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0152</v>
+        <v>-0.609</v>
       </c>
       <c r="E11">
-        <v>-0.0242</v>
+        <v>1.108</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1722,28 +1686,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>17.1</v>
+        <v>1.25</v>
       </c>
       <c r="L11">
-        <v>0.2310810810810811</v>
+        <v>0.1024590163934426</v>
       </c>
       <c r="M11">
-        <v>12.2</v>
+        <v>2.52</v>
       </c>
       <c r="N11">
-        <v>0.06538049303322616</v>
+        <v>0.1067796610169491</v>
       </c>
       <c r="O11">
-        <v>0.7134502923976607</v>
+        <v>2.016</v>
       </c>
       <c r="P11">
-        <v>12.2</v>
+        <v>2.52</v>
       </c>
       <c r="Q11">
-        <v>0.06538049303322616</v>
+        <v>0.1067796610169491</v>
       </c>
       <c r="R11">
-        <v>0.7134502923976607</v>
+        <v>2.016</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1752,61 +1716,64 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9.42</v>
+        <v>11.1</v>
       </c>
       <c r="V11">
-        <v>0.05048231511254019</v>
+        <v>0.4703389830508474</v>
       </c>
       <c r="W11">
-        <v>0.123021582733813</v>
+        <v>0.03180661577608142</v>
       </c>
       <c r="X11">
-        <v>0.1459735552471633</v>
+        <v>0.09024099499223337</v>
       </c>
       <c r="Y11">
-        <v>-0.02295197251335031</v>
+        <v>-0.05843437921615195</v>
       </c>
       <c r="Z11">
-        <v>0.09948910997579993</v>
+        <v>0.3202099737532808</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08299236487683384</v>
+        <v>0.07123121568290253</v>
       </c>
       <c r="AC11">
-        <v>-0.08299236487683384</v>
+        <v>-0.07123121568290253</v>
       </c>
       <c r="AD11">
-        <v>398.3</v>
+        <v>27</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>398.3</v>
+        <v>27</v>
       </c>
       <c r="AG11">
-        <v>388.88</v>
+        <v>15.9</v>
       </c>
       <c r="AH11">
-        <v>0.6809711061719953</v>
+        <v>0.5335968379446641</v>
       </c>
       <c r="AI11">
-        <v>0.7555007587253414</v>
+        <v>0.4047976011994003</v>
       </c>
       <c r="AJ11">
-        <v>0.6757489400152915</v>
+        <v>0.4025316455696203</v>
       </c>
       <c r="AK11">
-        <v>0.7510525705898258</v>
+        <v>0.2859712230215827</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-2.37</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1817,7 +1784,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Country Group Holdings Public Company Limited (SET:CGH)</t>
+          <t>Trinity Watthana Public Company Limited (SET:TNITY)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1826,10 +1793,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.236</v>
-      </c>
-      <c r="E12">
-        <v>-0.104</v>
+        <v>-0.153</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1838,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.001411486977002307</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.001411486977002307</v>
       </c>
       <c r="K12">
-        <v>2.95</v>
+        <v>-7.61</v>
       </c>
       <c r="L12">
-        <v>0.07248157248157248</v>
+        <v>-1.101302460202605</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1856,7 +1820,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1865,61 +1829,61 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>24.3</v>
+        <v>2.29</v>
       </c>
       <c r="V12">
-        <v>0.3131443298969073</v>
+        <v>0.09123505976095617</v>
       </c>
       <c r="W12">
-        <v>0.01710144927536232</v>
+        <v>-0.1710112359550562</v>
       </c>
       <c r="X12">
-        <v>0.101234012530035</v>
+        <v>0.1614601974791212</v>
       </c>
       <c r="Y12">
-        <v>-0.08413256325467264</v>
+        <v>-0.3324714334341773</v>
       </c>
       <c r="Z12">
-        <v>0.206494165398275</v>
+        <v>0.04312517519360126</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>6.087062316671111e-05</v>
       </c>
       <c r="AB12">
-        <v>0.08380201145306046</v>
+        <v>0.0741888958122794</v>
       </c>
       <c r="AC12">
-        <v>-0.08380201145306046</v>
+        <v>-0.07412802518911268</v>
       </c>
       <c r="AD12">
-        <v>56</v>
+        <v>111.9</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.0112331249445703</v>
       </c>
       <c r="AF12">
-        <v>56</v>
+        <v>111.9112331249446</v>
       </c>
       <c r="AG12">
-        <v>31.7</v>
+        <v>109.6212331249446</v>
       </c>
       <c r="AH12">
-        <v>0.4191616766467066</v>
+        <v>0.8168033421237033</v>
       </c>
       <c r="AI12">
-        <v>0.2650260293421675</v>
+        <v>0.7445300713614635</v>
       </c>
       <c r="AJ12">
-        <v>0.2900274473924977</v>
+        <v>0.8136893538027409</v>
       </c>
       <c r="AK12">
-        <v>0.1695187165775401</v>
+        <v>0.7405777590868562</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1927,133 +1891,11 @@
       <c r="AM12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Trinity Watthana Public Company Limited (SET:TNITY)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0471</v>
-      </c>
-      <c r="E13">
-        <v>0.425</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0.0005017216279114492</v>
-      </c>
-      <c r="J13">
-        <v>0.0004129493967486019</v>
-      </c>
-      <c r="K13">
-        <v>5.21</v>
-      </c>
-      <c r="L13">
-        <v>0.2480952380952381</v>
-      </c>
-      <c r="M13">
-        <v>5.25</v>
-      </c>
-      <c r="N13">
-        <v>0.1209677419354839</v>
-      </c>
-      <c r="O13">
-        <v>1.00767754318618</v>
-      </c>
-      <c r="P13">
-        <v>5.25</v>
-      </c>
-      <c r="Q13">
-        <v>0.1209677419354839</v>
-      </c>
-      <c r="R13">
-        <v>1.00767754318618</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>2.03</v>
-      </c>
-      <c r="V13">
-        <v>0.04677419354838709</v>
-      </c>
-      <c r="W13">
-        <v>0.1039920159680639</v>
-      </c>
-      <c r="X13">
-        <v>0.1652973906156521</v>
-      </c>
-      <c r="Y13">
-        <v>-0.06130537464758826</v>
-      </c>
-      <c r="Z13">
-        <v>0.1343292295768305</v>
-      </c>
-      <c r="AA13">
-        <v>5.547117431945661e-05</v>
-      </c>
-      <c r="AB13">
-        <v>0.0878593481048511</v>
-      </c>
-      <c r="AC13">
-        <v>-0.08780387693053164</v>
-      </c>
-      <c r="AD13">
-        <v>119.1</v>
-      </c>
-      <c r="AE13">
-        <v>0.02231922906929783</v>
-      </c>
-      <c r="AF13">
-        <v>119.1223192290693</v>
-      </c>
-      <c r="AG13">
-        <v>117.0923192290693</v>
-      </c>
-      <c r="AH13">
-        <v>0.7329597546609626</v>
-      </c>
-      <c r="AI13">
-        <v>0.7280322133944298</v>
-      </c>
-      <c r="AJ13">
-        <v>0.7295820746533324</v>
-      </c>
-      <c r="AK13">
-        <v>0.7246156239832297</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>7940</v>
-      </c>
-      <c r="AP13">
-        <v>7806.154615271286</v>
+      <c r="AN12">
+        <v>9325</v>
+      </c>
+      <c r="AP12">
+        <v>9135.102760412046</v>
       </c>
     </row>
   </sheetData>
